--- a/event_registration_forms/031_plant_protein_consortium_registration_form--event_registration_forms.xlsx
+++ b/event_registration_forms/031_plant_protein_consortium_registration_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-member'}</t>
+          <t>non-member</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Member'}</t>
+          <t>Non-Member</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sponsor'}</t>
+          <t>sponsor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sponsor'}</t>
+          <t>Sponsor</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'i_have_read_and_agree_to_the_terms_and_conditions',_'value':_1}</t>
+          <t>i_have_read_and_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'I have read and agree to the terms and conditions', 'value': 1}</t>
+          <t>I have read and agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'i_have_not_read_and_do_not_agree_to_the_terms_and_conditions',_'value':_2}</t>
+          <t>i_have_not_read_and_do_not_agree_to_the_terms_and_conditions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'I have not read and do not agree to the terms and conditions', 'value': 2}</t>
+          <t>I have not read and do not agree to the terms and conditions</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_provided',_'value':_3}</t>
+          <t>not_provided</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Provided', 'value': 3}</t>
+          <t>Not Provided</t>
         </is>
       </c>
     </row>
